--- a/Analisis CFBC MAYO-JUNIO.xlsx
+++ b/Analisis CFBC MAYO-JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yisus\Desktop\APLICACION CHOFERES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986B1B6D-232C-4110-8DDE-FFBBDA950B1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FBE737-8DC0-4CBD-8086-2F15AAEADAA9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="58">
   <si>
     <t>Salida</t>
   </si>
@@ -759,7 +759,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L851"/>
+  <dimension ref="A1:L905"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="11" bestFit="1" customWidth="1"/>
@@ -25406,7 +25406,7 @@
         <v>177</v>
       </c>
       <c r="L837" s="9">
-        <f t="shared" ref="L837:L851" si="14">K837*J837</f>
+        <f t="shared" ref="L837:L900" si="14">K837*J837</f>
         <v>3186</v>
       </c>
     </row>
@@ -25814,6 +25814,1572 @@
       <c r="L851" s="9">
         <f t="shared" si="14"/>
         <v>1512</v>
+      </c>
+    </row>
+    <row r="852" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A852" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F852" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G852, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G852" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H852" s="2">
+        <v>816</v>
+      </c>
+      <c r="I852" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J852" s="4">
+        <v>8</v>
+      </c>
+      <c r="K852" s="8">
+        <f>IFERROR(VLOOKUP(I852, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L852" s="9">
+        <f t="shared" si="14"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="853" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A853" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F853" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G853, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G853" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H853" s="2">
+        <v>816</v>
+      </c>
+      <c r="I853" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J853" s="4">
+        <v>10</v>
+      </c>
+      <c r="K853" s="8">
+        <f>IFERROR(VLOOKUP(I853, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L853" s="9">
+        <f t="shared" si="14"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="854" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A854" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F854" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G854, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G854" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H854" s="2">
+        <v>816</v>
+      </c>
+      <c r="I854" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J854" s="4">
+        <v>8</v>
+      </c>
+      <c r="K854" s="8">
+        <f>IFERROR(VLOOKUP(I854, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L854" s="9">
+        <f t="shared" si="14"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="855" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A855" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F855" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G855, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G855" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H855" s="2">
+        <v>816</v>
+      </c>
+      <c r="I855" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J855" s="4">
+        <v>6</v>
+      </c>
+      <c r="K855" s="8">
+        <f>IFERROR(VLOOKUP(I855, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L855" s="9">
+        <f t="shared" si="14"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="856" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A856" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F856" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G856, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G856" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H856" s="2">
+        <v>816</v>
+      </c>
+      <c r="I856" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J856" s="4">
+        <v>10</v>
+      </c>
+      <c r="K856" s="8">
+        <f>IFERROR(VLOOKUP(I856, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L856" s="9">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="857" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A857" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F857" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G857, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G857" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H857" s="2">
+        <v>816</v>
+      </c>
+      <c r="I857" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J857" s="4">
+        <v>16</v>
+      </c>
+      <c r="K857" s="8">
+        <f>IFERROR(VLOOKUP(I857, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L857" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="858" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A858" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F858" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G858, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PACIFICO</v>
+      </c>
+      <c r="G858" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H858" s="2">
+        <v>817</v>
+      </c>
+      <c r="I858" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J858" s="4">
+        <v>10</v>
+      </c>
+      <c r="K858" s="8">
+        <f>IFERROR(VLOOKUP(I858, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L858" s="9">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="859" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A859" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F859" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G859, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PACIFICO</v>
+      </c>
+      <c r="G859" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H859" s="2">
+        <v>817</v>
+      </c>
+      <c r="I859" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J859" s="4">
+        <v>16</v>
+      </c>
+      <c r="K859" s="8">
+        <f>IFERROR(VLOOKUP(I859, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L859" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="860" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A860" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F860" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G860, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G860" s="1">
+        <v>190</v>
+      </c>
+      <c r="H860" s="2">
+        <v>818</v>
+      </c>
+      <c r="I860" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J860" s="4">
+        <v>8</v>
+      </c>
+      <c r="K860" s="8">
+        <f>IFERROR(VLOOKUP(I860, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L860" s="9">
+        <f t="shared" si="14"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="861" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A861" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F861" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G861, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G861" s="1">
+        <v>190</v>
+      </c>
+      <c r="H861" s="2">
+        <v>818</v>
+      </c>
+      <c r="I861" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J861" s="4">
+        <v>8</v>
+      </c>
+      <c r="K861" s="8">
+        <f>IFERROR(VLOOKUP(I861, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L861" s="9">
+        <f t="shared" si="14"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="862" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A862" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F862" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G862, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G862" s="1">
+        <v>190</v>
+      </c>
+      <c r="H862" s="2">
+        <v>818</v>
+      </c>
+      <c r="I862" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J862" s="4">
+        <v>10</v>
+      </c>
+      <c r="K862" s="8">
+        <f>IFERROR(VLOOKUP(I862, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L862" s="9">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="863" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A863" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F863" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G863, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G863" s="1">
+        <v>190</v>
+      </c>
+      <c r="H863" s="2">
+        <v>818</v>
+      </c>
+      <c r="I863" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J863" s="4">
+        <v>16</v>
+      </c>
+      <c r="K863" s="8">
+        <f>IFERROR(VLOOKUP(I863, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L863" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="864" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A864" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F864" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G864, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G864" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H864" s="2">
+        <v>819</v>
+      </c>
+      <c r="I864" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J864" s="4">
+        <v>4</v>
+      </c>
+      <c r="K864" s="8">
+        <f>IFERROR(VLOOKUP(I864, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L864" s="9">
+        <f t="shared" si="14"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="865" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A865" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F865" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G865, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G865" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H865" s="2">
+        <v>819</v>
+      </c>
+      <c r="I865" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J865" s="4">
+        <v>6</v>
+      </c>
+      <c r="K865" s="8">
+        <f>IFERROR(VLOOKUP(I865, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L865" s="9">
+        <f t="shared" si="14"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="866" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A866" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F866" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G866, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G866" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H866" s="2">
+        <v>819</v>
+      </c>
+      <c r="I866" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J866" s="4">
+        <v>16</v>
+      </c>
+      <c r="K866" s="8">
+        <f>IFERROR(VLOOKUP(I866, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L866" s="9">
+        <f t="shared" si="14"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="867" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A867" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F867" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G867, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G867" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H867" s="2">
+        <v>819</v>
+      </c>
+      <c r="I867" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J867" s="4">
+        <v>10</v>
+      </c>
+      <c r="K867" s="8">
+        <f>IFERROR(VLOOKUP(I867, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L867" s="9">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="868" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A868" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F868" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G868, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G868" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H868" s="2">
+        <v>819</v>
+      </c>
+      <c r="I868" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J868" s="4">
+        <v>16</v>
+      </c>
+      <c r="K868" s="8">
+        <f>IFERROR(VLOOKUP(I868, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L868" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="869" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A869" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F869" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G869, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G869" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H869" s="2">
+        <v>820</v>
+      </c>
+      <c r="I869" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J869" s="4">
+        <v>4</v>
+      </c>
+      <c r="K869" s="8">
+        <f>IFERROR(VLOOKUP(I869, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L869" s="9">
+        <f t="shared" si="14"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="870" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A870" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F870" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G870, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G870" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H870" s="2">
+        <v>820</v>
+      </c>
+      <c r="I870" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J870" s="4">
+        <v>6</v>
+      </c>
+      <c r="K870" s="8">
+        <f>IFERROR(VLOOKUP(I870, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L870" s="9">
+        <f t="shared" si="14"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="871" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A871" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F871" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G871, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G871" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H871" s="2">
+        <v>820</v>
+      </c>
+      <c r="I871" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J871" s="4">
+        <v>8</v>
+      </c>
+      <c r="K871" s="8">
+        <f>IFERROR(VLOOKUP(I871, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L871" s="9">
+        <f t="shared" si="14"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="872" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A872" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F872" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G872, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G872" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H872" s="2">
+        <v>820</v>
+      </c>
+      <c r="I872" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J872" s="4">
+        <v>16</v>
+      </c>
+      <c r="K872" s="8">
+        <f>IFERROR(VLOOKUP(I872, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L872" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="873" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A873" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F873" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G873, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G873" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H873" s="2">
+        <v>821</v>
+      </c>
+      <c r="I873" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J873" s="4">
+        <v>4</v>
+      </c>
+      <c r="K873" s="8">
+        <f>IFERROR(VLOOKUP(I873, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L873" s="9">
+        <f t="shared" si="14"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="874" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A874" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F874" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G874, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G874" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H874" s="2">
+        <v>821</v>
+      </c>
+      <c r="I874" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J874" s="4">
+        <v>6</v>
+      </c>
+      <c r="K874" s="8">
+        <f>IFERROR(VLOOKUP(I874, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L874" s="9">
+        <f t="shared" si="14"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="875" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A875" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F875" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G875, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G875" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H875" s="2">
+        <v>821</v>
+      </c>
+      <c r="I875" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J875" s="4">
+        <v>8</v>
+      </c>
+      <c r="K875" s="8">
+        <f>IFERROR(VLOOKUP(I875, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L875" s="9">
+        <f t="shared" si="14"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="876" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A876" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F876" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G876, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G876" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H876" s="2">
+        <v>821</v>
+      </c>
+      <c r="I876" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J876" s="4">
+        <v>10</v>
+      </c>
+      <c r="K876" s="8">
+        <f>IFERROR(VLOOKUP(I876, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L876" s="9">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="877" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A877" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F877" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G877, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G877" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H877" s="2">
+        <v>821</v>
+      </c>
+      <c r="I877" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J877" s="4">
+        <v>16</v>
+      </c>
+      <c r="K877" s="8">
+        <f>IFERROR(VLOOKUP(I877, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L877" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="878" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A878" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F878" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G878, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G878" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H878" s="2">
+        <v>822</v>
+      </c>
+      <c r="I878" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J878" s="4">
+        <v>8</v>
+      </c>
+      <c r="K878" s="8">
+        <f>IFERROR(VLOOKUP(I878, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L878" s="9">
+        <f t="shared" si="14"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="879" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A879" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F879" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G879, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G879" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H879" s="2">
+        <v>822</v>
+      </c>
+      <c r="I879" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J879" s="4">
+        <v>8</v>
+      </c>
+      <c r="K879" s="8">
+        <f>IFERROR(VLOOKUP(I879, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L879" s="9">
+        <f t="shared" si="14"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="880" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A880" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F880" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G880, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G880" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H880" s="2">
+        <v>822</v>
+      </c>
+      <c r="I880" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J880" s="4">
+        <v>10</v>
+      </c>
+      <c r="K880" s="8">
+        <f>IFERROR(VLOOKUP(I880, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L880" s="9">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="881" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A881" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F881" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G881, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G881" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H881" s="2">
+        <v>822</v>
+      </c>
+      <c r="I881" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J881" s="4">
+        <v>16</v>
+      </c>
+      <c r="K881" s="8">
+        <f>IFERROR(VLOOKUP(I881, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L881" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="882" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A882" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F882" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G882, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G882" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H882" s="2">
+        <v>823</v>
+      </c>
+      <c r="I882" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J882" s="4">
+        <v>8</v>
+      </c>
+      <c r="K882" s="8">
+        <f>IFERROR(VLOOKUP(I882, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L882" s="9">
+        <f t="shared" si="14"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="883" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A883" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F883" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G883, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G883" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H883" s="2">
+        <v>823</v>
+      </c>
+      <c r="I883" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J883" s="4">
+        <v>10</v>
+      </c>
+      <c r="K883" s="8">
+        <f>IFERROR(VLOOKUP(I883, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L883" s="9">
+        <f t="shared" si="14"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="884" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A884" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F884" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G884, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G884" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H884" s="2">
+        <v>823</v>
+      </c>
+      <c r="I884" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J884" s="4">
+        <v>8</v>
+      </c>
+      <c r="K884" s="8">
+        <f>IFERROR(VLOOKUP(I884, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L884" s="9">
+        <f t="shared" si="14"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="885" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A885" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F885" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G885, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G885" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H885" s="2">
+        <v>823</v>
+      </c>
+      <c r="I885" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J885" s="4">
+        <v>20</v>
+      </c>
+      <c r="K885" s="8">
+        <f>IFERROR(VLOOKUP(I885, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L885" s="9">
+        <f t="shared" si="14"/>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="886" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A886" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F886" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G886, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G886" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H886" s="2">
+        <v>823</v>
+      </c>
+      <c r="I886" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J886" s="4">
+        <v>16</v>
+      </c>
+      <c r="K886" s="8">
+        <f>IFERROR(VLOOKUP(I886, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L886" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="887" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A887" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F887" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G887, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G887" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H887" s="2">
+        <v>824</v>
+      </c>
+      <c r="I887" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J887" s="4">
+        <v>8</v>
+      </c>
+      <c r="K887" s="8">
+        <f>IFERROR(VLOOKUP(I887, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L887" s="9">
+        <f t="shared" si="14"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="888" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A888" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F888" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G888, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G888" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H888" s="2">
+        <v>824</v>
+      </c>
+      <c r="I888" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J888" s="4">
+        <v>10</v>
+      </c>
+      <c r="K888" s="8">
+        <f>IFERROR(VLOOKUP(I888, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L888" s="9">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="889" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A889" s="54">
+        <v>46205</v>
+      </c>
+      <c r="F889" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G889, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G889" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H889" s="2">
+        <v>824</v>
+      </c>
+      <c r="I889" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J889" s="4">
+        <v>16</v>
+      </c>
+      <c r="K889" s="8">
+        <f>IFERROR(VLOOKUP(I889, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L889" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="890" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A890" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F890" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G890, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G890" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H890" s="2">
+        <v>825</v>
+      </c>
+      <c r="I890" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J890" s="4">
+        <v>8</v>
+      </c>
+      <c r="K890" s="8">
+        <f>IFERROR(VLOOKUP(I890, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L890" s="9">
+        <f t="shared" si="14"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="891" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A891" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F891" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G891, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G891" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H891" s="2">
+        <v>826</v>
+      </c>
+      <c r="I891" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J891" s="4">
+        <v>4</v>
+      </c>
+      <c r="K891" s="8">
+        <f>IFERROR(VLOOKUP(I891, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L891" s="9">
+        <f t="shared" si="14"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="892" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A892" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F892" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G892, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G892" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H892" s="2">
+        <v>826</v>
+      </c>
+      <c r="I892" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J892" s="4">
+        <v>6</v>
+      </c>
+      <c r="K892" s="8">
+        <f>IFERROR(VLOOKUP(I892, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L892" s="9">
+        <f t="shared" si="14"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="893" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A893" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F893" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G893, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G893" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H893" s="2">
+        <v>827</v>
+      </c>
+      <c r="I893" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J893" s="4">
+        <v>4</v>
+      </c>
+      <c r="K893" s="8">
+        <f>IFERROR(VLOOKUP(I893, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L893" s="9">
+        <f t="shared" si="14"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="894" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A894" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F894" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G894, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G894" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H894" s="2">
+        <v>827</v>
+      </c>
+      <c r="I894" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J894" s="4">
+        <v>6</v>
+      </c>
+      <c r="K894" s="8">
+        <f>IFERROR(VLOOKUP(I894, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L894" s="9">
+        <f t="shared" si="14"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="895" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A895" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F895" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G895, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G895" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H895" s="2">
+        <v>828</v>
+      </c>
+      <c r="I895" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J895" s="4">
+        <v>4</v>
+      </c>
+      <c r="K895" s="8">
+        <f>IFERROR(VLOOKUP(I895, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L895" s="9">
+        <f t="shared" si="14"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="896" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A896" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F896" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G896, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G896" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H896" s="2">
+        <v>828</v>
+      </c>
+      <c r="I896" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J896" s="4">
+        <v>6</v>
+      </c>
+      <c r="K896" s="8">
+        <f>IFERROR(VLOOKUP(I896, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L896" s="9">
+        <f t="shared" si="14"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="897" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A897" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F897" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G897, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G897" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H897" s="2">
+        <v>829</v>
+      </c>
+      <c r="I897" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J897" s="4">
+        <v>10</v>
+      </c>
+      <c r="K897" s="8">
+        <f>IFERROR(VLOOKUP(I897, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L897" s="9">
+        <f t="shared" si="14"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="898" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A898" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F898" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G898, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G898" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H898" s="2">
+        <v>829</v>
+      </c>
+      <c r="I898" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J898" s="4">
+        <v>8</v>
+      </c>
+      <c r="K898" s="8">
+        <f>IFERROR(VLOOKUP(I898, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L898" s="9">
+        <f t="shared" si="14"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="899" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A899" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F899" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G899, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G899" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H899" s="2">
+        <v>829</v>
+      </c>
+      <c r="I899" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J899" s="4">
+        <v>10</v>
+      </c>
+      <c r="K899" s="8">
+        <f>IFERROR(VLOOKUP(I899, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L899" s="9">
+        <f t="shared" si="14"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="900" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A900" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F900" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G900, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G900" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H900" s="2">
+        <v>829</v>
+      </c>
+      <c r="I900" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J900" s="4">
+        <v>16</v>
+      </c>
+      <c r="K900" s="8">
+        <f>IFERROR(VLOOKUP(I900, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L900" s="9">
+        <f t="shared" si="14"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="901" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A901" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F901" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G901, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G901" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H901" s="2">
+        <v>830</v>
+      </c>
+      <c r="I901" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J901" s="4">
+        <v>4</v>
+      </c>
+      <c r="K901" s="8">
+        <f>IFERROR(VLOOKUP(I901, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L901" s="9">
+        <f t="shared" ref="L901:L905" si="15">K901*J901</f>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="902" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A902" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F902" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G902, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G902" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H902" s="2">
+        <v>830</v>
+      </c>
+      <c r="I902" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J902" s="4">
+        <v>6</v>
+      </c>
+      <c r="K902" s="8">
+        <f>IFERROR(VLOOKUP(I902, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L902" s="9">
+        <f t="shared" si="15"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="903" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A903" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F903" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G903, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G903" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H903" s="2">
+        <v>830</v>
+      </c>
+      <c r="I903" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J903" s="4">
+        <v>8</v>
+      </c>
+      <c r="K903" s="8">
+        <f>IFERROR(VLOOKUP(I903, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L903" s="9">
+        <f t="shared" si="15"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="904" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A904" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F904" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G904, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G904" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H904" s="2">
+        <v>830</v>
+      </c>
+      <c r="I904" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J904" s="4">
+        <v>10</v>
+      </c>
+      <c r="K904" s="8">
+        <f>IFERROR(VLOOKUP(I904, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L904" s="9">
+        <f t="shared" si="15"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="905" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A905" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F905" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G905, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G905" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H905" s="2">
+        <v>830</v>
+      </c>
+      <c r="I905" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J905" s="4">
+        <v>16</v>
+      </c>
+      <c r="K905" s="8">
+        <f>IFERROR(VLOOKUP(I905, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L905" s="9">
+        <f t="shared" si="15"/>
+        <v>1008</v>
       </c>
     </row>
   </sheetData>

--- a/Analisis CFBC MAYO-JUNIO.xlsx
+++ b/Analisis CFBC MAYO-JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yisus\Desktop\APLICACION CHOFERES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84E1C5D-69DE-4B6C-AB35-7BF0946B906C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A529A8-A4BC-4441-A258-BCAEE40B1389}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="58">
   <si>
     <t>Salida</t>
   </si>
@@ -796,7 +796,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L1616"/>
+  <dimension ref="A1:L1838"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="11" bestFit="1" customWidth="1"/>
@@ -47715,7 +47715,7 @@
         <v>113</v>
       </c>
       <c r="L1605" s="9">
-        <f t="shared" ref="L1605:L1616" si="26">K1605*J1605</f>
+        <f t="shared" ref="L1605:L1668" si="26">K1605*J1605</f>
         <v>678</v>
       </c>
     </row>
@@ -48035,6 +48035,6444 @@
       </c>
       <c r="L1616" s="9">
         <f t="shared" si="26"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1617" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1617" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1617, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PACIFICO</v>
+      </c>
+      <c r="G1617" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H1617" s="4">
+        <v>1017</v>
+      </c>
+      <c r="I1617" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1617" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1617" s="8">
+        <f>IFERROR(VLOOKUP(I1617, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1617" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1618" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1618" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1618, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PACIFICO</v>
+      </c>
+      <c r="G1618" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H1618" s="4">
+        <v>1017</v>
+      </c>
+      <c r="I1618" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1618" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1618" s="8">
+        <f>IFERROR(VLOOKUP(I1618, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1618" s="9">
+        <f t="shared" si="26"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1619" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1619" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1619, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1619" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1619" s="4">
+        <v>1018</v>
+      </c>
+      <c r="I1619" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1619" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1619" s="8">
+        <f>IFERROR(VLOOKUP(I1619, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1619" s="9">
+        <f t="shared" si="26"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1620" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1620" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1620, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1620" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1620" s="4">
+        <v>1018</v>
+      </c>
+      <c r="I1620" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1620" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1620" s="8">
+        <f>IFERROR(VLOOKUP(I1620, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1620" s="9">
+        <f t="shared" si="26"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1621" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1621" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1621, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1621" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1621" s="4">
+        <v>1018</v>
+      </c>
+      <c r="I1621" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1621" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1621" s="8">
+        <f>IFERROR(VLOOKUP(I1621, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1621" s="9">
+        <f t="shared" si="26"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1622" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1622" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1622, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1622" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1622" s="4">
+        <v>1018</v>
+      </c>
+      <c r="I1622" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1622" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1622" s="8">
+        <f>IFERROR(VLOOKUP(I1622, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1622" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1623" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1623" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1623, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1623" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1623" s="4">
+        <v>1018</v>
+      </c>
+      <c r="I1623" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1623" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1623" s="8">
+        <f>IFERROR(VLOOKUP(I1623, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1623" s="9">
+        <f t="shared" si="26"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1624" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1624" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1624, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1624" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1624" s="4">
+        <v>1019</v>
+      </c>
+      <c r="I1624" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1624" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1624" s="8">
+        <f>IFERROR(VLOOKUP(I1624, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1624" s="9">
+        <f t="shared" si="26"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1625" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1625" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1625, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1625" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1625" s="4">
+        <v>1019</v>
+      </c>
+      <c r="I1625" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1625" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1625" s="8">
+        <f>IFERROR(VLOOKUP(I1625, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1625" s="9">
+        <f t="shared" si="26"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1626" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1626" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1626, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1626" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1626" s="4">
+        <v>1019</v>
+      </c>
+      <c r="I1626" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1626" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1626" s="8">
+        <f>IFERROR(VLOOKUP(I1626, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1626" s="9">
+        <f t="shared" si="26"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1627" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1627" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1627, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1627" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1627" s="4">
+        <v>1019</v>
+      </c>
+      <c r="I1627" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1627" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1627" s="8">
+        <f>IFERROR(VLOOKUP(I1627, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1627" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1628" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1628" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1628, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1628" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1628" s="4">
+        <v>1019</v>
+      </c>
+      <c r="I1628" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1628" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1628" s="8">
+        <f>IFERROR(VLOOKUP(I1628, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1628" s="9">
+        <f t="shared" si="26"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1629" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1629" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1629, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1629" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1629" s="4">
+        <v>1020</v>
+      </c>
+      <c r="I1629" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1629" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1629" s="8">
+        <f>IFERROR(VLOOKUP(I1629, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1629" s="9">
+        <f t="shared" si="26"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1630" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1630" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1630, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1630" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1630" s="4">
+        <v>1020</v>
+      </c>
+      <c r="I1630" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1630" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1630" s="8">
+        <f>IFERROR(VLOOKUP(I1630, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1630" s="9">
+        <f t="shared" si="26"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1631" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1631" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1631, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1631" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1631" s="4">
+        <v>1020</v>
+      </c>
+      <c r="I1631" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1631" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1631" s="8">
+        <f>IFERROR(VLOOKUP(I1631, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1631" s="9">
+        <f t="shared" si="26"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1632" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1632" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1632, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1632" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1632" s="4">
+        <v>1020</v>
+      </c>
+      <c r="I1632" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1632" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1632" s="8">
+        <f>IFERROR(VLOOKUP(I1632, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1632" s="9">
+        <f t="shared" si="26"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1633" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1633" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1633, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1633" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1633" s="4">
+        <v>1020</v>
+      </c>
+      <c r="I1633" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1633" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1633" s="8">
+        <f>IFERROR(VLOOKUP(I1633, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1633" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1634" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1634" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1634, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1634" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1634" s="4">
+        <v>1020</v>
+      </c>
+      <c r="I1634" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1634" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1634" s="8">
+        <f>IFERROR(VLOOKUP(I1634, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1634" s="9">
+        <f t="shared" si="26"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1635" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1635" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1635, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1635" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1635" s="4">
+        <v>1021</v>
+      </c>
+      <c r="I1635" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1635" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1635" s="8">
+        <f>IFERROR(VLOOKUP(I1635, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1635" s="9">
+        <f t="shared" si="26"/>
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1636" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1636" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1636, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1636" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1636" s="4">
+        <v>1021</v>
+      </c>
+      <c r="I1636" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1636" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1636" s="8">
+        <f>IFERROR(VLOOKUP(I1636, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1636" s="9">
+        <f t="shared" si="26"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1637" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1637" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1637, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1637" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1637" s="4">
+        <v>1021</v>
+      </c>
+      <c r="I1637" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1637" s="4">
+        <v>12</v>
+      </c>
+      <c r="K1637" s="8">
+        <f>IFERROR(VLOOKUP(I1637, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1637" s="9">
+        <f t="shared" si="26"/>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1638" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1638" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1638, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1638" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1638" s="4">
+        <v>1021</v>
+      </c>
+      <c r="I1638" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1638" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1638" s="8">
+        <f>IFERROR(VLOOKUP(I1638, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1638" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1639" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1639" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1639, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1639" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1639" s="4">
+        <v>1021</v>
+      </c>
+      <c r="I1639" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1639" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1639" s="8">
+        <f>IFERROR(VLOOKUP(I1639, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1639" s="9">
+        <f t="shared" si="26"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1640" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1640" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1640, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1640" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1640" s="4">
+        <v>1022</v>
+      </c>
+      <c r="I1640" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1640" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1640" s="8">
+        <f>IFERROR(VLOOKUP(I1640, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1640" s="9">
+        <f t="shared" si="26"/>
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1641" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1641" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1641, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1641" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1641" s="4">
+        <v>1022</v>
+      </c>
+      <c r="I1641" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1641" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1641" s="8">
+        <f>IFERROR(VLOOKUP(I1641, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1641" s="9">
+        <f t="shared" si="26"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1642" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1642" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1642, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1642" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1642" s="4">
+        <v>1022</v>
+      </c>
+      <c r="I1642" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1642" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1642" s="8">
+        <f>IFERROR(VLOOKUP(I1642, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1642" s="9">
+        <f t="shared" si="26"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1643" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1643" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1643, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1643" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1643" s="4">
+        <v>1022</v>
+      </c>
+      <c r="I1643" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1643" s="4">
+        <v>12</v>
+      </c>
+      <c r="K1643" s="8">
+        <f>IFERROR(VLOOKUP(I1643, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1643" s="9">
+        <f t="shared" si="26"/>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1644" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1644" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1644, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1644" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1644" s="4">
+        <v>1022</v>
+      </c>
+      <c r="I1644" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1644" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1644" s="8">
+        <f>IFERROR(VLOOKUP(I1644, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1644" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1645" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1645" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1645, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1645" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1645" s="4">
+        <v>1022</v>
+      </c>
+      <c r="I1645" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1645" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1645" s="8">
+        <f>IFERROR(VLOOKUP(I1645, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1645" s="9">
+        <f t="shared" si="26"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1646" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1646" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1646, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1646" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1646" s="4">
+        <v>1023</v>
+      </c>
+      <c r="I1646" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1646" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1646" s="8">
+        <f>IFERROR(VLOOKUP(I1646, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1646" s="9">
+        <f t="shared" si="26"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1647" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1647" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1647, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1647" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1647" s="4">
+        <v>1023</v>
+      </c>
+      <c r="I1647" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1647" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1647" s="8">
+        <f>IFERROR(VLOOKUP(I1647, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1647" s="9">
+        <f t="shared" si="26"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1648" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1648" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1648, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1648" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1648" s="4">
+        <v>1023</v>
+      </c>
+      <c r="I1648" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1648" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1648" s="8">
+        <f>IFERROR(VLOOKUP(I1648, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1648" s="9">
+        <f t="shared" si="26"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1649" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1649" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1649, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1649" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1649" s="4">
+        <v>1023</v>
+      </c>
+      <c r="I1649" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1649" s="4">
+        <v>12</v>
+      </c>
+      <c r="K1649" s="8">
+        <f>IFERROR(VLOOKUP(I1649, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1649" s="9">
+        <f t="shared" si="26"/>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1650" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1650" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1650, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1650" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1650" s="4">
+        <v>1023</v>
+      </c>
+      <c r="I1650" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1650" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1650" s="8">
+        <f>IFERROR(VLOOKUP(I1650, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1650" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1651" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1651" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1651, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1651" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1651" s="4">
+        <v>1023</v>
+      </c>
+      <c r="I1651" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1651" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1651" s="8">
+        <f>IFERROR(VLOOKUP(I1651, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1651" s="9">
+        <f t="shared" si="26"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1652" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1652" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1652, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1652" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1652" s="4">
+        <v>1024</v>
+      </c>
+      <c r="I1652" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1652" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1652" s="8">
+        <f>IFERROR(VLOOKUP(I1652, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1652" s="9">
+        <f t="shared" si="26"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1653" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1653" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1653, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1653" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1653" s="4">
+        <v>1024</v>
+      </c>
+      <c r="I1653" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1653" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1653" s="8">
+        <f>IFERROR(VLOOKUP(I1653, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1653" s="9">
+        <f t="shared" si="26"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1654" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1654" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1654, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1654" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1654" s="4">
+        <v>1024</v>
+      </c>
+      <c r="I1654" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1654" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1654" s="8">
+        <f>IFERROR(VLOOKUP(I1654, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1654" s="9">
+        <f t="shared" si="26"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1655" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1655" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1655, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1655" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1655" s="4">
+        <v>1024</v>
+      </c>
+      <c r="I1655" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1655" s="4">
+        <v>18</v>
+      </c>
+      <c r="K1655" s="8">
+        <f>IFERROR(VLOOKUP(I1655, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1655" s="9">
+        <f t="shared" si="26"/>
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1656" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1656" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1656, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1656" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1656" s="4">
+        <v>1024</v>
+      </c>
+      <c r="I1656" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1656" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1656" s="8">
+        <f>IFERROR(VLOOKUP(I1656, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1656" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1657" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1657" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1657, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1657" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1657" s="4">
+        <v>1024</v>
+      </c>
+      <c r="I1657" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1657" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1657" s="8">
+        <f>IFERROR(VLOOKUP(I1657, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1657" s="9">
+        <f t="shared" si="26"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1658" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1658" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1658, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1658" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1658" s="4">
+        <v>1025</v>
+      </c>
+      <c r="I1658" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1658" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1658" s="8">
+        <f>IFERROR(VLOOKUP(I1658, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1658" s="9">
+        <f t="shared" si="26"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1659" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1659" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1659, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1659" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1659" s="4">
+        <v>1025</v>
+      </c>
+      <c r="I1659" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1659" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1659" s="8">
+        <f>IFERROR(VLOOKUP(I1659, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1659" s="9">
+        <f t="shared" si="26"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1660" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1660" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1660, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1660" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1660" s="4">
+        <v>1025</v>
+      </c>
+      <c r="I1660" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1660" s="4">
+        <v>24</v>
+      </c>
+      <c r="K1660" s="8">
+        <f>IFERROR(VLOOKUP(I1660, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1660" s="9">
+        <f t="shared" si="26"/>
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1661" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1661" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1661, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1661" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1661" s="4">
+        <v>1025</v>
+      </c>
+      <c r="I1661" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1661" s="4">
+        <v>36</v>
+      </c>
+      <c r="K1661" s="8">
+        <f>IFERROR(VLOOKUP(I1661, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1661" s="9">
+        <f t="shared" si="26"/>
+        <v>6372</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1662" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F1662" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1662, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1662" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1662" s="4">
+        <v>1025</v>
+      </c>
+      <c r="I1662" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1662" s="4">
+        <v>32</v>
+      </c>
+      <c r="K1662" s="8">
+        <f>IFERROR(VLOOKUP(I1662, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1662" s="9">
+        <f t="shared" si="26"/>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1663" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1663" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1663, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1663" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1663" s="4">
+        <v>1026</v>
+      </c>
+      <c r="I1663" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1663" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1663" s="8">
+        <f>IFERROR(VLOOKUP(I1663, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1663" s="9">
+        <f t="shared" si="26"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1664" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1664" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1664, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1664" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1664" s="4">
+        <v>1026</v>
+      </c>
+      <c r="I1664" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1664" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1664" s="8">
+        <f>IFERROR(VLOOKUP(I1664, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1664" s="9">
+        <f t="shared" si="26"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1665" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1665" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1665, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1665" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1665" s="4">
+        <v>1026</v>
+      </c>
+      <c r="I1665" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1665" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1665" s="8">
+        <f>IFERROR(VLOOKUP(I1665, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1665" s="9">
+        <f t="shared" si="26"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1666" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1666" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1666, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1666" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1666" s="4">
+        <v>1026</v>
+      </c>
+      <c r="I1666" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1666" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1666" s="8">
+        <f>IFERROR(VLOOKUP(I1666, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1666" s="9">
+        <f t="shared" si="26"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1667" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1667" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1667, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1667" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1667" s="4">
+        <v>1026</v>
+      </c>
+      <c r="I1667" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1667" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1667" s="8">
+        <f>IFERROR(VLOOKUP(I1667, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1667" s="9">
+        <f t="shared" si="26"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1668" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1668" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1668, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1668" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1668" s="4">
+        <v>1027</v>
+      </c>
+      <c r="I1668" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1668" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1668" s="8">
+        <f>IFERROR(VLOOKUP(I1668, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1668" s="9">
+        <f t="shared" si="26"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1669" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1669" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1669, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1669" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1669" s="4">
+        <v>1027</v>
+      </c>
+      <c r="I1669" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1669" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1669" s="8">
+        <f>IFERROR(VLOOKUP(I1669, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1669" s="9">
+        <f t="shared" ref="L1669:L1732" si="27">K1669*J1669</f>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1670" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1670" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1670, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1670" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1670" s="4">
+        <v>1027</v>
+      </c>
+      <c r="I1670" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1670" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1670" s="8">
+        <f>IFERROR(VLOOKUP(I1670, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1670" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1671" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1671" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1671, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1671" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1671" s="4">
+        <v>1027</v>
+      </c>
+      <c r="I1671" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1671" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1671" s="8">
+        <f>IFERROR(VLOOKUP(I1671, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1671" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1672" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1672" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1672, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1672" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1672" s="4">
+        <v>1028</v>
+      </c>
+      <c r="I1672" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1672" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1672" s="8">
+        <f>IFERROR(VLOOKUP(I1672, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1672" s="9">
+        <f t="shared" si="27"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1673" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1673" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1673, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1673" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1673" s="4">
+        <v>1028</v>
+      </c>
+      <c r="I1673" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1673" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1673" s="8">
+        <f>IFERROR(VLOOKUP(I1673, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1673" s="9">
+        <f t="shared" si="27"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1674" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1674" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1674, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1674" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1674" s="4">
+        <v>1028</v>
+      </c>
+      <c r="I1674" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1674" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1674" s="8">
+        <f>IFERROR(VLOOKUP(I1674, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1674" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1675" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1675" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1675, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1675" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1675" s="4">
+        <v>1028</v>
+      </c>
+      <c r="I1675" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1675" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1675" s="8">
+        <f>IFERROR(VLOOKUP(I1675, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1675" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1676" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1676" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1676, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1676" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1676" s="4">
+        <v>1028</v>
+      </c>
+      <c r="I1676" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1676" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1676" s="8">
+        <f>IFERROR(VLOOKUP(I1676, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1676" s="9">
+        <f t="shared" si="27"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1677" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1677" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1677, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1677" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1677" s="4">
+        <v>1029</v>
+      </c>
+      <c r="I1677" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1677" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1677" s="8">
+        <f>IFERROR(VLOOKUP(I1677, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1677" s="9">
+        <f t="shared" si="27"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1678" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1678" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1678, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1678" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1678" s="4">
+        <v>1029</v>
+      </c>
+      <c r="I1678" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1678" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1678" s="8">
+        <f>IFERROR(VLOOKUP(I1678, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1678" s="9">
+        <f t="shared" si="27"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1679" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1679" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1679, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1679" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1679" s="4">
+        <v>1029</v>
+      </c>
+      <c r="I1679" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1679" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1679" s="8">
+        <f>IFERROR(VLOOKUP(I1679, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1679" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1680" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1680" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1680, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1680" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1680" s="4">
+        <v>1029</v>
+      </c>
+      <c r="I1680" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1680" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1680" s="8">
+        <f>IFERROR(VLOOKUP(I1680, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1680" s="9">
+        <f t="shared" si="27"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1681" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1681" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1681, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1681" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1681" s="4">
+        <v>1029</v>
+      </c>
+      <c r="I1681" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1681" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1681" s="8">
+        <f>IFERROR(VLOOKUP(I1681, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1681" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1682" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1682" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1682, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1682" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1682" s="4">
+        <v>1029</v>
+      </c>
+      <c r="I1682" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1682" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1682" s="8">
+        <f>IFERROR(VLOOKUP(I1682, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1682" s="9">
+        <f t="shared" si="27"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1683" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1683" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1683, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1683" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1683" s="4">
+        <v>1030</v>
+      </c>
+      <c r="I1683" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1683" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1683" s="8">
+        <f>IFERROR(VLOOKUP(I1683, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1683" s="9">
+        <f t="shared" si="27"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1684" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1684" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1684, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1684" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1684" s="4">
+        <v>1030</v>
+      </c>
+      <c r="I1684" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1684" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1684" s="8">
+        <f>IFERROR(VLOOKUP(I1684, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1684" s="9">
+        <f t="shared" si="27"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1685" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1685" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1685, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1685" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1685" s="4">
+        <v>1030</v>
+      </c>
+      <c r="I1685" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1685" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1685" s="8">
+        <f>IFERROR(VLOOKUP(I1685, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1685" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1686" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1686" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1686, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1686" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1686" s="4">
+        <v>1030</v>
+      </c>
+      <c r="I1686" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1686" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1686" s="8">
+        <f>IFERROR(VLOOKUP(I1686, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1686" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1687" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1687" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1687, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1687" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1687" s="4">
+        <v>1030</v>
+      </c>
+      <c r="I1687" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1687" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1687" s="8">
+        <f>IFERROR(VLOOKUP(I1687, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1687" s="9">
+        <f t="shared" si="27"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1688" s="54">
+        <v>46247</v>
+      </c>
+      <c r="F1688" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1688, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G1688" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H1688" s="4">
+        <v>1031</v>
+      </c>
+      <c r="I1688" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1688" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1688" s="8">
+        <f>IFERROR(VLOOKUP(I1688, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1688" s="9">
+        <f t="shared" si="27"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1689" s="54">
+        <v>46248</v>
+      </c>
+      <c r="F1689" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1689, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1689" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1689" s="4">
+        <v>1032</v>
+      </c>
+      <c r="I1689" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1689" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1689" s="8">
+        <f>IFERROR(VLOOKUP(I1689, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1689" s="9">
+        <f t="shared" si="27"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1690" s="54">
+        <v>46248</v>
+      </c>
+      <c r="F1690" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1690, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1690" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1690" s="4">
+        <v>1032</v>
+      </c>
+      <c r="I1690" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1690" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1690" s="8">
+        <f>IFERROR(VLOOKUP(I1690, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1690" s="9">
+        <f t="shared" si="27"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1691" s="54">
+        <v>46248</v>
+      </c>
+      <c r="F1691" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1691, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1691" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1691" s="4">
+        <v>1032</v>
+      </c>
+      <c r="I1691" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1691" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1691" s="8">
+        <f>IFERROR(VLOOKUP(I1691, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1691" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1692" s="54">
+        <v>46248</v>
+      </c>
+      <c r="F1692" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1692, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1692" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1692" s="4">
+        <v>1032</v>
+      </c>
+      <c r="I1692" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1692" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1692" s="8">
+        <f>IFERROR(VLOOKUP(I1692, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1692" s="9">
+        <f t="shared" si="27"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1693" s="54">
+        <v>46248</v>
+      </c>
+      <c r="F1693" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1693, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1693" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1693" s="4">
+        <v>1032</v>
+      </c>
+      <c r="I1693" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1693" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1693" s="8">
+        <f>IFERROR(VLOOKUP(I1693, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1693" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1694" s="54">
+        <v>46248</v>
+      </c>
+      <c r="F1694" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1694, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1694" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1694" s="4">
+        <v>1032</v>
+      </c>
+      <c r="I1694" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1694" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1694" s="8">
+        <f>IFERROR(VLOOKUP(I1694, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1694" s="9">
+        <f t="shared" si="27"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1695" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1695" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1695, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G1695" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H1695" s="4">
+        <v>1033</v>
+      </c>
+      <c r="I1695" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1695" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1695" s="8">
+        <f>IFERROR(VLOOKUP(I1695, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1695" s="9">
+        <f t="shared" si="27"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1696" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1696" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1696, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G1696" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H1696" s="4">
+        <v>1033</v>
+      </c>
+      <c r="I1696" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1696" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1696" s="8">
+        <f>IFERROR(VLOOKUP(I1696, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1696" s="9">
+        <f t="shared" si="27"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1697" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1697" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1697, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G1697" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H1697" s="4">
+        <v>1033</v>
+      </c>
+      <c r="I1697" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1697" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1697" s="8">
+        <f>IFERROR(VLOOKUP(I1697, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1697" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1698" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1698" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1698, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G1698" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H1698" s="4">
+        <v>1033</v>
+      </c>
+      <c r="I1698" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1698" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1698" s="8">
+        <f>IFERROR(VLOOKUP(I1698, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1698" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1699" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1699" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1699, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1699" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1699" s="4">
+        <v>1034</v>
+      </c>
+      <c r="I1699" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1699" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1699" s="8">
+        <f>IFERROR(VLOOKUP(I1699, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1699" s="9">
+        <f t="shared" si="27"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1700" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1700" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1700, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1700" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1700" s="4">
+        <v>1034</v>
+      </c>
+      <c r="I1700" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1700" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1700" s="8">
+        <f>IFERROR(VLOOKUP(I1700, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1700" s="9">
+        <f t="shared" si="27"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1701" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1701" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1701, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1701" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1701" s="4">
+        <v>1034</v>
+      </c>
+      <c r="I1701" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1701" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1701" s="8">
+        <f>IFERROR(VLOOKUP(I1701, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1701" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1702" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1702" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1702, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1702" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1702" s="4">
+        <v>1034</v>
+      </c>
+      <c r="I1702" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1702" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1702" s="8">
+        <f>IFERROR(VLOOKUP(I1702, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1702" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1703" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1703" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1703, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1703" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1703" s="4">
+        <v>1034</v>
+      </c>
+      <c r="I1703" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1703" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1703" s="8">
+        <f>IFERROR(VLOOKUP(I1703, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1703" s="9">
+        <f t="shared" si="27"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1704" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1704" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1704, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1704" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1704" s="4">
+        <v>1035</v>
+      </c>
+      <c r="I1704" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1704" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1704" s="8">
+        <f>IFERROR(VLOOKUP(I1704, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1704" s="9">
+        <f t="shared" si="27"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1705" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1705" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1705, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1705" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1705" s="4">
+        <v>1035</v>
+      </c>
+      <c r="I1705" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1705" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1705" s="8">
+        <f>IFERROR(VLOOKUP(I1705, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1705" s="9">
+        <f t="shared" si="27"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1706" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1706" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1706, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1706" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1706" s="4">
+        <v>1035</v>
+      </c>
+      <c r="I1706" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1706" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1706" s="8">
+        <f>IFERROR(VLOOKUP(I1706, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1706" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1707" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1707" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1707, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1707" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1707" s="4">
+        <v>1035</v>
+      </c>
+      <c r="I1707" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1707" s="4">
+        <v>12</v>
+      </c>
+      <c r="K1707" s="8">
+        <f>IFERROR(VLOOKUP(I1707, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1707" s="9">
+        <f t="shared" si="27"/>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1708" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1708" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1708, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1708" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1708" s="4">
+        <v>1035</v>
+      </c>
+      <c r="I1708" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1708" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1708" s="8">
+        <f>IFERROR(VLOOKUP(I1708, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1708" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1709" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1709" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1709, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1709" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1709" s="4">
+        <v>1035</v>
+      </c>
+      <c r="I1709" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1709" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1709" s="8">
+        <f>IFERROR(VLOOKUP(I1709, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1709" s="9">
+        <f t="shared" si="27"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1710" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1710" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1710, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1710" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1710" s="4">
+        <v>1036</v>
+      </c>
+      <c r="I1710" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1710" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1710" s="8">
+        <f>IFERROR(VLOOKUP(I1710, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1710" s="9">
+        <f t="shared" si="27"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1711" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1711" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1711, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1711" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1711" s="4">
+        <v>1036</v>
+      </c>
+      <c r="I1711" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1711" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1711" s="8">
+        <f>IFERROR(VLOOKUP(I1711, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1711" s="9">
+        <f t="shared" si="27"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1712" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1712" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1712, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1712" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1712" s="4">
+        <v>1036</v>
+      </c>
+      <c r="I1712" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1712" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1712" s="8">
+        <f>IFERROR(VLOOKUP(I1712, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1712" s="9">
+        <f t="shared" si="27"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1713" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1713" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1713, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1713" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1713" s="4">
+        <v>1036</v>
+      </c>
+      <c r="I1713" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1713" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1713" s="8">
+        <f>IFERROR(VLOOKUP(I1713, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1713" s="9">
+        <f t="shared" si="27"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1714" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1714" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1714, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PACIFICO</v>
+      </c>
+      <c r="G1714" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H1714" s="4">
+        <v>1037</v>
+      </c>
+      <c r="I1714" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1714" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1714" s="8">
+        <f>IFERROR(VLOOKUP(I1714, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1714" s="9">
+        <f t="shared" si="27"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1715" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1715" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1715, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1715" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1715" s="4">
+        <v>1038</v>
+      </c>
+      <c r="I1715" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1715" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1715" s="8">
+        <f>IFERROR(VLOOKUP(I1715, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1715" s="9">
+        <f t="shared" si="27"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1716" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1716" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1716, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1716" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1716" s="4">
+        <v>1038</v>
+      </c>
+      <c r="I1716" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1716" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1716" s="8">
+        <f>IFERROR(VLOOKUP(I1716, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1716" s="9">
+        <f t="shared" si="27"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1717" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1717" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1717, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1717" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1717" s="4">
+        <v>1038</v>
+      </c>
+      <c r="I1717" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1717" s="4">
+        <v>24</v>
+      </c>
+      <c r="K1717" s="8">
+        <f>IFERROR(VLOOKUP(I1717, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1717" s="9">
+        <f t="shared" si="27"/>
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1718" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1718" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1718, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1718" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1718" s="4">
+        <v>1038</v>
+      </c>
+      <c r="I1718" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1718" s="4">
+        <v>18</v>
+      </c>
+      <c r="K1718" s="8">
+        <f>IFERROR(VLOOKUP(I1718, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1718" s="9">
+        <f t="shared" si="27"/>
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1719" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1719" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1719, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1719" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1719" s="4">
+        <v>1038</v>
+      </c>
+      <c r="I1719" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1719" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1719" s="8">
+        <f>IFERROR(VLOOKUP(I1719, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1719" s="9">
+        <f t="shared" si="27"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1720" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1720" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1720, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1720" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1720" s="4">
+        <v>1039</v>
+      </c>
+      <c r="I1720" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1720" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1720" s="8">
+        <f>IFERROR(VLOOKUP(I1720, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1720" s="9">
+        <f t="shared" si="27"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1721" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1721" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1721, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1721" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1721" s="4">
+        <v>1039</v>
+      </c>
+      <c r="I1721" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1721" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1721" s="8">
+        <f>IFERROR(VLOOKUP(I1721, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1721" s="9">
+        <f t="shared" si="27"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1722" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1722" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1722, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1722" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1722" s="4">
+        <v>1039</v>
+      </c>
+      <c r="I1722" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1722" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1722" s="8">
+        <f>IFERROR(VLOOKUP(I1722, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1722" s="9">
+        <f t="shared" si="27"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1723" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1723" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1723, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1723" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1723" s="4">
+        <v>1039</v>
+      </c>
+      <c r="I1723" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1723" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1723" s="8">
+        <f>IFERROR(VLOOKUP(I1723, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1723" s="9">
+        <f t="shared" si="27"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1724" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1724" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1724, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1724" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1724" s="4">
+        <v>1040</v>
+      </c>
+      <c r="I1724" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1724" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1724" s="8">
+        <f>IFERROR(VLOOKUP(I1724, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1724" s="9">
+        <f t="shared" si="27"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1725" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1725" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1725, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1725" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1725" s="4">
+        <v>1040</v>
+      </c>
+      <c r="I1725" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1725" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1725" s="8">
+        <f>IFERROR(VLOOKUP(I1725, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1725" s="9">
+        <f t="shared" si="27"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1726" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1726" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1726, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1726" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1726" s="4">
+        <v>1040</v>
+      </c>
+      <c r="I1726" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1726" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1726" s="8">
+        <f>IFERROR(VLOOKUP(I1726, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1726" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1727" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1727" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1727, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1727" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1727" s="4">
+        <v>1040</v>
+      </c>
+      <c r="I1727" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1727" s="4">
+        <v>12</v>
+      </c>
+      <c r="K1727" s="8">
+        <f>IFERROR(VLOOKUP(I1727, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1727" s="9">
+        <f t="shared" si="27"/>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1728" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1728" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1728, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1728" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1728" s="4">
+        <v>1040</v>
+      </c>
+      <c r="I1728" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1728" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1728" s="8">
+        <f>IFERROR(VLOOKUP(I1728, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1728" s="9">
+        <f t="shared" si="27"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1729" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1729" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1729, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1729" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1729" s="4">
+        <v>1040</v>
+      </c>
+      <c r="I1729" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1729" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1729" s="8">
+        <f>IFERROR(VLOOKUP(I1729, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1729" s="9">
+        <f t="shared" si="27"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1730" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1730" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1730, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1730" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1730" s="4">
+        <v>1041</v>
+      </c>
+      <c r="I1730" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1730" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1730" s="8">
+        <f>IFERROR(VLOOKUP(I1730, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1730" s="9">
+        <f t="shared" si="27"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1731" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1731" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1731, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1731" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1731" s="4">
+        <v>1041</v>
+      </c>
+      <c r="I1731" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1731" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1731" s="8">
+        <f>IFERROR(VLOOKUP(I1731, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1731" s="9">
+        <f t="shared" si="27"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1732" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1732" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1732, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1732" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1732" s="4">
+        <v>1041</v>
+      </c>
+      <c r="I1732" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1732" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1732" s="8">
+        <f>IFERROR(VLOOKUP(I1732, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1732" s="9">
+        <f t="shared" si="27"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1733" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1733" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1733, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1733" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1733" s="4">
+        <v>1041</v>
+      </c>
+      <c r="I1733" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1733" s="4">
+        <v>12</v>
+      </c>
+      <c r="K1733" s="8">
+        <f>IFERROR(VLOOKUP(I1733, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1733" s="9">
+        <f t="shared" ref="L1733:L1796" si="28">K1733*J1733</f>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1734" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1734" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1734, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1734" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1734" s="4">
+        <v>1041</v>
+      </c>
+      <c r="I1734" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1734" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1734" s="8">
+        <f>IFERROR(VLOOKUP(I1734, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1734" s="9">
+        <f t="shared" si="28"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1735" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1735" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1735, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1735" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1735" s="4">
+        <v>1042</v>
+      </c>
+      <c r="I1735" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1735" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1735" s="8">
+        <f>IFERROR(VLOOKUP(I1735, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1735" s="9">
+        <f t="shared" si="28"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1736" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1736" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1736, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1736" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1736" s="4">
+        <v>1042</v>
+      </c>
+      <c r="I1736" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1736" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1736" s="8">
+        <f>IFERROR(VLOOKUP(I1736, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1736" s="9">
+        <f t="shared" si="28"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1737" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1737" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1737, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1737" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1737" s="4">
+        <v>1042</v>
+      </c>
+      <c r="I1737" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1737" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1737" s="8">
+        <f>IFERROR(VLOOKUP(I1737, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1737" s="9">
+        <f t="shared" si="28"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1738" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1738" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1738, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1738" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1738" s="4">
+        <v>1042</v>
+      </c>
+      <c r="I1738" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1738" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1738" s="8">
+        <f>IFERROR(VLOOKUP(I1738, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1738" s="9">
+        <f t="shared" si="28"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1739" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1739" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1739, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1739" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1739" s="4">
+        <v>1042</v>
+      </c>
+      <c r="I1739" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1739" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1739" s="8">
+        <f>IFERROR(VLOOKUP(I1739, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1739" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1740" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1740" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1740, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1740" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1740" s="4">
+        <v>1043</v>
+      </c>
+      <c r="I1740" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1740" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1740" s="8">
+        <f>IFERROR(VLOOKUP(I1740, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1740" s="9">
+        <f t="shared" si="28"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1741" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1741" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1741, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1741" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1741" s="4">
+        <v>1043</v>
+      </c>
+      <c r="I1741" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1741" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1741" s="8">
+        <f>IFERROR(VLOOKUP(I1741, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1741" s="9">
+        <f t="shared" si="28"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1742" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1742" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1742, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1742" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1742" s="4">
+        <v>1043</v>
+      </c>
+      <c r="I1742" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1742" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1742" s="8">
+        <f>IFERROR(VLOOKUP(I1742, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1742" s="9">
+        <f t="shared" si="28"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1743" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1743" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1743, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1743" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1743" s="4">
+        <v>1043</v>
+      </c>
+      <c r="I1743" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1743" s="4">
+        <v>12</v>
+      </c>
+      <c r="K1743" s="8">
+        <f>IFERROR(VLOOKUP(I1743, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1743" s="9">
+        <f t="shared" si="28"/>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1744" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1744" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1744, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1744" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1744" s="4">
+        <v>1043</v>
+      </c>
+      <c r="I1744" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1744" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1744" s="8">
+        <f>IFERROR(VLOOKUP(I1744, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1744" s="9">
+        <f t="shared" si="28"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1745" s="54">
+        <v>46249</v>
+      </c>
+      <c r="F1745" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1745, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1745" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1745" s="4">
+        <v>1043</v>
+      </c>
+      <c r="I1745" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1745" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1745" s="8">
+        <f>IFERROR(VLOOKUP(I1745, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1745" s="9">
+        <f t="shared" si="28"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1746" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1746" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1746, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1746" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1746" s="4">
+        <v>1044</v>
+      </c>
+      <c r="I1746" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1746" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1746" s="8">
+        <f>IFERROR(VLOOKUP(I1746, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1746" s="9">
+        <f t="shared" si="28"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1747" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1747" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1747, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1747" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1747" s="4">
+        <v>1044</v>
+      </c>
+      <c r="I1747" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1747" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1747" s="8">
+        <f>IFERROR(VLOOKUP(I1747, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1747" s="9">
+        <f t="shared" si="28"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1748" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1748" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1748, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1748" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1748" s="4">
+        <v>1044</v>
+      </c>
+      <c r="I1748" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1748" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1748" s="8">
+        <f>IFERROR(VLOOKUP(I1748, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1748" s="9">
+        <f t="shared" si="28"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1749" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1749" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1749, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1749" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1749" s="4">
+        <v>1044</v>
+      </c>
+      <c r="I1749" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1749" s="4">
+        <v>12</v>
+      </c>
+      <c r="K1749" s="8">
+        <f>IFERROR(VLOOKUP(I1749, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1749" s="9">
+        <f t="shared" si="28"/>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1750" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1750" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1750, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1750" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1750" s="4">
+        <v>1044</v>
+      </c>
+      <c r="I1750" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1750" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1750" s="8">
+        <f>IFERROR(VLOOKUP(I1750, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1750" s="9">
+        <f t="shared" si="28"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1751" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1751" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1751, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1751" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1751" s="4">
+        <v>1044</v>
+      </c>
+      <c r="I1751" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1751" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1751" s="8">
+        <f>IFERROR(VLOOKUP(I1751, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1751" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1752" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1752" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1752, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1752" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1752" s="4">
+        <v>1046</v>
+      </c>
+      <c r="I1752" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1752" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1752" s="8">
+        <f>IFERROR(VLOOKUP(I1752, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1752" s="9">
+        <f t="shared" si="28"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1753" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1753" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1753, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1753" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1753" s="4">
+        <v>1046</v>
+      </c>
+      <c r="I1753" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1753" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1753" s="8">
+        <f>IFERROR(VLOOKUP(I1753, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1753" s="9">
+        <f t="shared" si="28"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1754" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1754" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1754, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1754" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1754" s="4">
+        <v>1046</v>
+      </c>
+      <c r="I1754" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1754" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1754" s="8">
+        <f>IFERROR(VLOOKUP(I1754, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1754" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1755" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1755" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1755, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1755" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1755" s="4">
+        <v>1047</v>
+      </c>
+      <c r="I1755" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1755" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1755" s="8">
+        <f>IFERROR(VLOOKUP(I1755, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1755" s="9">
+        <f t="shared" si="28"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1756" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1756" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1756, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1756" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1756" s="4">
+        <v>1047</v>
+      </c>
+      <c r="I1756" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1756" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1756" s="8">
+        <f>IFERROR(VLOOKUP(I1756, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1756" s="9">
+        <f t="shared" si="28"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1757" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1757" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1757, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1757" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1757" s="4">
+        <v>1047</v>
+      </c>
+      <c r="I1757" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1757" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1757" s="8">
+        <f>IFERROR(VLOOKUP(I1757, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1757" s="9">
+        <f t="shared" si="28"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1758" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1758" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1758, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1758" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1758" s="4">
+        <v>1047</v>
+      </c>
+      <c r="I1758" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1758" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1758" s="8">
+        <f>IFERROR(VLOOKUP(I1758, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1758" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1759" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1759" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1759, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1759" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1759" s="4">
+        <v>1048</v>
+      </c>
+      <c r="I1759" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1759" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1759" s="8">
+        <f>IFERROR(VLOOKUP(I1759, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1759" s="9">
+        <f t="shared" si="28"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1760" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1760" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1760, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1760" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1760" s="4">
+        <v>1048</v>
+      </c>
+      <c r="I1760" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1760" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1760" s="8">
+        <f>IFERROR(VLOOKUP(I1760, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1760" s="9">
+        <f t="shared" si="28"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1761" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1761" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1761, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1761" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1761" s="4">
+        <v>1048</v>
+      </c>
+      <c r="I1761" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1761" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1761" s="8">
+        <f>IFERROR(VLOOKUP(I1761, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1761" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1762" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1762" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1762, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1762" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1762" s="4">
+        <v>1049</v>
+      </c>
+      <c r="I1762" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1762" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1762" s="8">
+        <f>IFERROR(VLOOKUP(I1762, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1762" s="9">
+        <f t="shared" si="28"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1763" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1763" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1763, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1763" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1763" s="4">
+        <v>1049</v>
+      </c>
+      <c r="I1763" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1763" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1763" s="8">
+        <f>IFERROR(VLOOKUP(I1763, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1763" s="9">
+        <f t="shared" si="28"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1764" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1764" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1764, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1764" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1764" s="4">
+        <v>1049</v>
+      </c>
+      <c r="I1764" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1764" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1764" s="8">
+        <f>IFERROR(VLOOKUP(I1764, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1764" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1765" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1765" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1765, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1765" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1765" s="4">
+        <v>1050</v>
+      </c>
+      <c r="I1765" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1765" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1765" s="8">
+        <f>IFERROR(VLOOKUP(I1765, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1765" s="9">
+        <f t="shared" si="28"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1766" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1766" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1766, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1766" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1766" s="4">
+        <v>1050</v>
+      </c>
+      <c r="I1766" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1766" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1766" s="8">
+        <f>IFERROR(VLOOKUP(I1766, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1766" s="9">
+        <f t="shared" si="28"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1767" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1767" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1767, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1767" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1767" s="4">
+        <v>1050</v>
+      </c>
+      <c r="I1767" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1767" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1767" s="8">
+        <f>IFERROR(VLOOKUP(I1767, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1767" s="9">
+        <f t="shared" si="28"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1768" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1768" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1768, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1768" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1768" s="4">
+        <v>1050</v>
+      </c>
+      <c r="I1768" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1768" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1768" s="8">
+        <f>IFERROR(VLOOKUP(I1768, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1768" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1769" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1769" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1769, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1769" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1769" s="4">
+        <v>1051</v>
+      </c>
+      <c r="I1769" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1769" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1769" s="8">
+        <f>IFERROR(VLOOKUP(I1769, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1769" s="9">
+        <f t="shared" si="28"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1770" s="54">
+        <v>46251</v>
+      </c>
+      <c r="F1770" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1770, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1770" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1770" s="4">
+        <v>1051</v>
+      </c>
+      <c r="I1770" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1770" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1770" s="8">
+        <f>IFERROR(VLOOKUP(I1770, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1770" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1771" s="54">
+        <v>46252</v>
+      </c>
+      <c r="F1771" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1771, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1771" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1771" s="4">
+        <v>1052</v>
+      </c>
+      <c r="I1771" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1771" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1771" s="8">
+        <f>IFERROR(VLOOKUP(I1771, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1771" s="9">
+        <f t="shared" si="28"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1772" s="54">
+        <v>46252</v>
+      </c>
+      <c r="F1772" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1772, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1772" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1772" s="4">
+        <v>1052</v>
+      </c>
+      <c r="I1772" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1772" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1772" s="8">
+        <f>IFERROR(VLOOKUP(I1772, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1772" s="9">
+        <f t="shared" si="28"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1773" s="54">
+        <v>46252</v>
+      </c>
+      <c r="F1773" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1773, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1773" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1773" s="4">
+        <v>1052</v>
+      </c>
+      <c r="I1773" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1773" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1773" s="8">
+        <f>IFERROR(VLOOKUP(I1773, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1773" s="9">
+        <f t="shared" si="28"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1774" s="54">
+        <v>46252</v>
+      </c>
+      <c r="F1774" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1774, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA</v>
+      </c>
+      <c r="G1774" s="1">
+        <v>3015</v>
+      </c>
+      <c r="H1774" s="4">
+        <v>1052</v>
+      </c>
+      <c r="I1774" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1774" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1774" s="8">
+        <f>IFERROR(VLOOKUP(I1774, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1774" s="9">
+        <f t="shared" si="28"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1775" s="54">
+        <v>46252</v>
+      </c>
+      <c r="F1775" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1775, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G1775" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H1775" s="4">
+        <v>1053</v>
+      </c>
+      <c r="I1775" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1775" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1775" s="8">
+        <f>IFERROR(VLOOKUP(I1775, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1775" s="9">
+        <f t="shared" si="28"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1776" s="54">
+        <v>46252</v>
+      </c>
+      <c r="F1776" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1776, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ENSENADA CENTRO</v>
+      </c>
+      <c r="G1776" s="1">
+        <v>2947</v>
+      </c>
+      <c r="H1776" s="4">
+        <v>1053</v>
+      </c>
+      <c r="I1776" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1776" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1776" s="8">
+        <f>IFERROR(VLOOKUP(I1776, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1776" s="9">
+        <f t="shared" si="28"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1777" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1777" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1777, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1777" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1777" s="4">
+        <v>1055</v>
+      </c>
+      <c r="I1777" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1777" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1777" s="8">
+        <f>IFERROR(VLOOKUP(I1777, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1777" s="9">
+        <f t="shared" si="28"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1778" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1778" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1778, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1778" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1778" s="4">
+        <v>1055</v>
+      </c>
+      <c r="I1778" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1778" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1778" s="8">
+        <f>IFERROR(VLOOKUP(I1778, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1778" s="9">
+        <f t="shared" si="28"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1779" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1779" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1779, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1779" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1779" s="4">
+        <v>1055</v>
+      </c>
+      <c r="I1779" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1779" s="4">
+        <v>18</v>
+      </c>
+      <c r="K1779" s="8">
+        <f>IFERROR(VLOOKUP(I1779, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1779" s="9">
+        <f t="shared" si="28"/>
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1780" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1780" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1780, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1780" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1780" s="4">
+        <v>1055</v>
+      </c>
+      <c r="I1780" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1780" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1780" s="8">
+        <f>IFERROR(VLOOKUP(I1780, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1780" s="9">
+        <f t="shared" si="28"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1781" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1781" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1781, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC NUEVO MEXICALI</v>
+      </c>
+      <c r="G1781" s="1">
+        <v>5041</v>
+      </c>
+      <c r="H1781" s="4">
+        <v>1055</v>
+      </c>
+      <c r="I1781" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1781" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1781" s="8">
+        <f>IFERROR(VLOOKUP(I1781, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1781" s="9">
+        <f t="shared" si="28"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1782" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1782" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1782, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1782" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1782" s="4">
+        <v>1056</v>
+      </c>
+      <c r="I1782" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1782" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1782" s="8">
+        <f>IFERROR(VLOOKUP(I1782, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1782" s="9">
+        <f t="shared" si="28"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1783" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1783" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1783, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1783" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1783" s="4">
+        <v>1056</v>
+      </c>
+      <c r="I1783" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1783" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1783" s="8">
+        <f>IFERROR(VLOOKUP(I1783, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1783" s="9">
+        <f t="shared" si="28"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1784" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1784" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1784, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1784" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1784" s="4">
+        <v>1056</v>
+      </c>
+      <c r="I1784" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1784" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1784" s="8">
+        <f>IFERROR(VLOOKUP(I1784, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1784" s="9">
+        <f t="shared" si="28"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1785" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1785" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1785, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC ROSARITO</v>
+      </c>
+      <c r="G1785" s="1">
+        <v>4187</v>
+      </c>
+      <c r="H1785" s="4">
+        <v>1056</v>
+      </c>
+      <c r="I1785" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1785" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1785" s="8">
+        <f>IFERROR(VLOOKUP(I1785, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1785" s="9">
+        <f t="shared" si="28"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1786" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1786" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1786, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1786" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1786" s="4">
+        <v>1057</v>
+      </c>
+      <c r="I1786" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1786" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1786" s="8">
+        <f>IFERROR(VLOOKUP(I1786, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1786" s="9">
+        <f t="shared" si="28"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1787" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1787" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1787, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1787" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1787" s="4">
+        <v>1057</v>
+      </c>
+      <c r="I1787" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1787" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1787" s="8">
+        <f>IFERROR(VLOOKUP(I1787, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1787" s="9">
+        <f t="shared" si="28"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1788" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1788" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1788, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1788" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1788" s="4">
+        <v>1057</v>
+      </c>
+      <c r="I1788" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1788" s="4">
+        <v>18</v>
+      </c>
+      <c r="K1788" s="8">
+        <f>IFERROR(VLOOKUP(I1788, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1788" s="9">
+        <f t="shared" si="28"/>
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1789" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1789" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1789, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1789" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1789" s="4">
+        <v>1057</v>
+      </c>
+      <c r="I1789" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1789" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1789" s="8">
+        <f>IFERROR(VLOOKUP(I1789, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1789" s="9">
+        <f t="shared" si="28"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1790" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1790" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1790, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC GALERIAS DEL VALLE</v>
+      </c>
+      <c r="G1790" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H1790" s="4">
+        <v>1057</v>
+      </c>
+      <c r="I1790" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1790" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1790" s="8">
+        <f>IFERROR(VLOOKUP(I1790, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1790" s="9">
+        <f t="shared" si="28"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1791" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1791" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1791, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1791" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1791" s="4">
+        <v>1058</v>
+      </c>
+      <c r="I1791" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1791" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1791" s="8">
+        <f>IFERROR(VLOOKUP(I1791, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1791" s="9">
+        <f t="shared" si="28"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1792" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1792" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1792, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1792" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1792" s="4">
+        <v>1058</v>
+      </c>
+      <c r="I1792" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1792" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1792" s="8">
+        <f>IFERROR(VLOOKUP(I1792, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1792" s="9">
+        <f t="shared" si="28"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1793" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1793" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1793, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1793" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1793" s="4">
+        <v>1058</v>
+      </c>
+      <c r="I1793" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1793" s="4">
+        <v>18</v>
+      </c>
+      <c r="K1793" s="8">
+        <f>IFERROR(VLOOKUP(I1793, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1793" s="9">
+        <f t="shared" si="28"/>
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1794" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1794" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1794, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1794" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1794" s="4">
+        <v>1058</v>
+      </c>
+      <c r="I1794" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1794" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1794" s="8">
+        <f>IFERROR(VLOOKUP(I1794, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1794" s="9">
+        <f t="shared" si="28"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1795" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1795" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1795, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI</v>
+      </c>
+      <c r="G1795" s="1">
+        <v>2304</v>
+      </c>
+      <c r="H1795" s="4">
+        <v>1058</v>
+      </c>
+      <c r="I1795" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1795" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1795" s="8">
+        <f>IFERROR(VLOOKUP(I1795, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1795" s="9">
+        <f t="shared" si="28"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1796" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1796" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1796, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1796" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1796" s="4">
+        <v>1059</v>
+      </c>
+      <c r="I1796" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1796" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1796" s="8">
+        <f>IFERROR(VLOOKUP(I1796, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1796" s="9">
+        <f t="shared" si="28"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1797" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1797" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1797, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1797" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1797" s="4">
+        <v>1059</v>
+      </c>
+      <c r="I1797" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1797" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1797" s="8">
+        <f>IFERROR(VLOOKUP(I1797, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1797" s="9">
+        <f t="shared" ref="L1797:L1838" si="29">K1797*J1797</f>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1798" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1798" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1798, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC LOMAS DE SANTA FE</v>
+      </c>
+      <c r="G1798" s="1">
+        <v>190</v>
+      </c>
+      <c r="H1798" s="4">
+        <v>1059</v>
+      </c>
+      <c r="I1798" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1798" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1798" s="8">
+        <f>IFERROR(VLOOKUP(I1798, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1798" s="9">
+        <f t="shared" si="29"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1799" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1799" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1799, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1799" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1799" s="4">
+        <v>1060</v>
+      </c>
+      <c r="I1799" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1799" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1799" s="8">
+        <f>IFERROR(VLOOKUP(I1799, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1799" s="9">
+        <f t="shared" si="29"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1800" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1800" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1800, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1800" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1800" s="4">
+        <v>1060</v>
+      </c>
+      <c r="I1800" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1800" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1800" s="8">
+        <f>IFERROR(VLOOKUP(I1800, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1800" s="9">
+        <f t="shared" si="29"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1801" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1801" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1801, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1801" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1801" s="4">
+        <v>1060</v>
+      </c>
+      <c r="I1801" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1801" s="4">
+        <v>24</v>
+      </c>
+      <c r="K1801" s="8">
+        <f>IFERROR(VLOOKUP(I1801, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1801" s="9">
+        <f t="shared" si="29"/>
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1802" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1802" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1802, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1802" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1802" s="4">
+        <v>1060</v>
+      </c>
+      <c r="I1802" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1802" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1802" s="8">
+        <f>IFERROR(VLOOKUP(I1802, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1802" s="9">
+        <f t="shared" si="29"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1803" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1803" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1803, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MEXICALI NOVENA</v>
+      </c>
+      <c r="G1803" s="1">
+        <v>1617</v>
+      </c>
+      <c r="H1803" s="4">
+        <v>1060</v>
+      </c>
+      <c r="I1803" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1803" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1803" s="8">
+        <f>IFERROR(VLOOKUP(I1803, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1803" s="9">
+        <f t="shared" si="29"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1804" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1804" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1804, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PACIFICO</v>
+      </c>
+      <c r="G1804" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H1804" s="4">
+        <v>1061</v>
+      </c>
+      <c r="I1804" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1804" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1804" s="8">
+        <f>IFERROR(VLOOKUP(I1804, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1804" s="9">
+        <f t="shared" si="29"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1805" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1805" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1805, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PACIFICO</v>
+      </c>
+      <c r="G1805" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H1805" s="4">
+        <v>1061</v>
+      </c>
+      <c r="I1805" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1805" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1805" s="8">
+        <f>IFERROR(VLOOKUP(I1805, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1805" s="9">
+        <f t="shared" si="29"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1806" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1806" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1806, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PACIFICO</v>
+      </c>
+      <c r="G1806" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H1806" s="4">
+        <v>1061</v>
+      </c>
+      <c r="I1806" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1806" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1806" s="8">
+        <f>IFERROR(VLOOKUP(I1806, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1806" s="9">
+        <f t="shared" si="29"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1807" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1807" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1807, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1807" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1807" s="4">
+        <v>1062</v>
+      </c>
+      <c r="I1807" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1807" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1807" s="8">
+        <f>IFERROR(VLOOKUP(I1807, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1807" s="9">
+        <f t="shared" si="29"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1808" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1808" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1808, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1808" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1808" s="4">
+        <v>1062</v>
+      </c>
+      <c r="I1808" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1808" s="4">
+        <v>15</v>
+      </c>
+      <c r="K1808" s="8">
+        <f>IFERROR(VLOOKUP(I1808, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1808" s="9">
+        <f t="shared" si="29"/>
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1809" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1809" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1809, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1809" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1809" s="4">
+        <v>1062</v>
+      </c>
+      <c r="I1809" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1809" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1809" s="8">
+        <f>IFERROR(VLOOKUP(I1809, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1809" s="9">
+        <f t="shared" si="29"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1810" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1810" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1810, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAYAS DE TIJUANA</v>
+      </c>
+      <c r="G1810" s="1">
+        <v>1613</v>
+      </c>
+      <c r="H1810" s="4">
+        <v>1062</v>
+      </c>
+      <c r="I1810" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1810" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1810" s="8">
+        <f>IFERROR(VLOOKUP(I1810, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1810" s="9">
+        <f t="shared" si="29"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1811" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1811" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1811, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1811" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1811" s="4">
+        <v>1063</v>
+      </c>
+      <c r="I1811" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1811" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1811" s="8">
+        <f>IFERROR(VLOOKUP(I1811, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1811" s="9">
+        <f t="shared" si="29"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1812" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1812" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1812, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1812" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1812" s="4">
+        <v>1063</v>
+      </c>
+      <c r="I1812" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1812" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1812" s="8">
+        <f>IFERROR(VLOOKUP(I1812, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1812" s="9">
+        <f t="shared" si="29"/>
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1813" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1813" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1813, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1813" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1813" s="4">
+        <v>1063</v>
+      </c>
+      <c r="I1813" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1813" s="4">
+        <v>18</v>
+      </c>
+      <c r="K1813" s="8">
+        <f>IFERROR(VLOOKUP(I1813, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1813" s="9">
+        <f t="shared" si="29"/>
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1814" s="54">
+        <v>46253</v>
+      </c>
+      <c r="F1814" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1814, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC PLAZA SAN PEDRO</v>
+      </c>
+      <c r="G1814" s="1">
+        <v>1140</v>
+      </c>
+      <c r="H1814" s="4">
+        <v>1063</v>
+      </c>
+      <c r="I1814" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1814" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1814" s="8">
+        <f>IFERROR(VLOOKUP(I1814, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1814" s="9">
+        <f t="shared" si="29"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1815" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1815" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1815, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1815" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1815" s="4">
+        <v>1064</v>
+      </c>
+      <c r="I1815" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1815" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1815" s="8">
+        <f>IFERROR(VLOOKUP(I1815, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1815" s="9">
+        <f t="shared" si="29"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1816" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1816" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1816, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1816" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1816" s="4">
+        <v>1064</v>
+      </c>
+      <c r="I1816" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1816" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1816" s="8">
+        <f>IFERROR(VLOOKUP(I1816, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1816" s="9">
+        <f t="shared" si="29"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1817" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1817" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1817, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1817" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1817" s="4">
+        <v>1064</v>
+      </c>
+      <c r="I1817" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1817" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1817" s="8">
+        <f>IFERROR(VLOOKUP(I1817, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1817" s="9">
+        <f t="shared" si="29"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1818" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1818" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1818, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TECATE GARITA</v>
+      </c>
+      <c r="G1818" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H1818" s="4">
+        <v>1064</v>
+      </c>
+      <c r="I1818" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1818" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1818" s="8">
+        <f>IFERROR(VLOOKUP(I1818, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1818" s="9">
+        <f t="shared" si="29"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1819" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1819" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1819, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1819" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1819" s="4">
+        <v>1065</v>
+      </c>
+      <c r="I1819" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1819" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1819" s="8">
+        <f>IFERROR(VLOOKUP(I1819, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1819" s="9">
+        <f t="shared" si="29"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1820" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1820" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1820, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1820" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1820" s="4">
+        <v>1065</v>
+      </c>
+      <c r="I1820" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1820" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1820" s="8">
+        <f>IFERROR(VLOOKUP(I1820, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1820" s="9">
+        <f t="shared" si="29"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1821" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1821" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1821, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1821" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1821" s="4">
+        <v>1065</v>
+      </c>
+      <c r="I1821" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1821" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1821" s="8">
+        <f>IFERROR(VLOOKUP(I1821, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1821" s="9">
+        <f t="shared" si="29"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1822" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1822" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1822, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1822" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1822" s="4">
+        <v>1065</v>
+      </c>
+      <c r="I1822" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1822" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1822" s="8">
+        <f>IFERROR(VLOOKUP(I1822, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1822" s="9">
+        <f t="shared" si="29"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1823" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1823" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1823, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA 2000</v>
+      </c>
+      <c r="G1823" s="1">
+        <v>4155</v>
+      </c>
+      <c r="H1823" s="4">
+        <v>1065</v>
+      </c>
+      <c r="I1823" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1823" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1823" s="8">
+        <f>IFERROR(VLOOKUP(I1823, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1823" s="9">
+        <f t="shared" si="29"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1824" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1824" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1824, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1824" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1824" s="4">
+        <v>1066</v>
+      </c>
+      <c r="I1824" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1824" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1824" s="8">
+        <f>IFERROR(VLOOKUP(I1824, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1824" s="9">
+        <f t="shared" si="29"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1825" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1825" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1825, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1825" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1825" s="4">
+        <v>1066</v>
+      </c>
+      <c r="I1825" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1825" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1825" s="8">
+        <f>IFERROR(VLOOKUP(I1825, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1825" s="9">
+        <f t="shared" si="29"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1826" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1826" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1826, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1826" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1826" s="4">
+        <v>1066</v>
+      </c>
+      <c r="I1826" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1826" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1826" s="8">
+        <f>IFERROR(VLOOKUP(I1826, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1826" s="9">
+        <f t="shared" si="29"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1827" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1827" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1827, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1827" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1827" s="4">
+        <v>1066</v>
+      </c>
+      <c r="I1827" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1827" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1827" s="8">
+        <f>IFERROR(VLOOKUP(I1827, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1827" s="9">
+        <f t="shared" si="29"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1828" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1828" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1828, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC TIJUANA HIPODROMO</v>
+      </c>
+      <c r="G1828" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H1828" s="4">
+        <v>1066</v>
+      </c>
+      <c r="I1828" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1828" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1828" s="8">
+        <f>IFERROR(VLOOKUP(I1828, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1828" s="9">
+        <f t="shared" si="29"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1829" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1829" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1829, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1829" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1829" s="4">
+        <v>1067</v>
+      </c>
+      <c r="I1829" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1829" s="4">
+        <v>4</v>
+      </c>
+      <c r="K1829" s="8">
+        <f>IFERROR(VLOOKUP(I1829, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1829" s="9">
+        <f t="shared" si="29"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1830" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1830" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1830, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1830" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1830" s="4">
+        <v>1067</v>
+      </c>
+      <c r="I1830" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1830" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1830" s="8">
+        <f>IFERROR(VLOOKUP(I1830, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1830" s="9">
+        <f t="shared" si="29"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1831" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1831" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1831, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1831" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1831" s="4">
+        <v>1067</v>
+      </c>
+      <c r="I1831" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1831" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1831" s="8">
+        <f>IFERROR(VLOOKUP(I1831, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1831" s="9">
+        <f t="shared" si="29"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1832" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1832" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1832, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1832" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1832" s="4">
+        <v>1067</v>
+      </c>
+      <c r="I1832" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1832" s="4">
+        <v>6</v>
+      </c>
+      <c r="K1832" s="8">
+        <f>IFERROR(VLOOKUP(I1832, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>177</v>
+      </c>
+      <c r="L1832" s="9">
+        <f t="shared" si="29"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1833" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1833" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1833, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1833" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1833" s="4">
+        <v>1067</v>
+      </c>
+      <c r="I1833" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1833" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1833" s="8">
+        <f>IFERROR(VLOOKUP(I1833, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>95</v>
+      </c>
+      <c r="L1833" s="9">
+        <f t="shared" si="29"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1834" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1834" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1834, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC DIAZ ORDAZ</v>
+      </c>
+      <c r="G1834" s="1">
+        <v>3664</v>
+      </c>
+      <c r="H1834" s="4">
+        <v>1067</v>
+      </c>
+      <c r="I1834" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1834" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1834" s="8">
+        <f>IFERROR(VLOOKUP(I1834, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1834" s="9">
+        <f t="shared" si="29"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1835" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1835" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1835, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1835" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1835" s="4">
+        <v>1068</v>
+      </c>
+      <c r="I1835" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1835" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1835" s="8">
+        <f>IFERROR(VLOOKUP(I1835, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>167</v>
+      </c>
+      <c r="L1835" s="9">
+        <f t="shared" si="29"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1836" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1836" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1836, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1836" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1836" s="4">
+        <v>1068</v>
+      </c>
+      <c r="I1836" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1836" s="4">
+        <v>10</v>
+      </c>
+      <c r="K1836" s="8">
+        <f>IFERROR(VLOOKUP(I1836, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>113</v>
+      </c>
+      <c r="L1836" s="9">
+        <f t="shared" si="29"/>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1837" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1837" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1837, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1837" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1837" s="4">
+        <v>1068</v>
+      </c>
+      <c r="I1837" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1837" s="4">
+        <v>8</v>
+      </c>
+      <c r="K1837" s="8">
+        <f>IFERROR(VLOOKUP(I1837, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>151</v>
+      </c>
+      <c r="L1837" s="9">
+        <f t="shared" si="29"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1838" s="54">
+        <v>46254</v>
+      </c>
+      <c r="F1838" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G1838, data!A:B, 2, FALSE), "Tienda")</f>
+        <v>SC MACROPLAZA INSURGENTES</v>
+      </c>
+      <c r="G1838" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1838" s="4">
+        <v>1068</v>
+      </c>
+      <c r="I1838" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1838" s="4">
+        <v>16</v>
+      </c>
+      <c r="K1838" s="8">
+        <f>IFERROR(VLOOKUP(I1838, data!E:F, 2, FALSE), "Precio Unidad")</f>
+        <v>63</v>
+      </c>
+      <c r="L1838" s="9">
+        <f t="shared" si="29"/>
         <v>1008</v>
       </c>
     </row>
